--- a/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot-2024-06-hand.xlsx
+++ b/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot-2024-06-hand.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\data-tidy\hack-tianyan\hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692A37E8-864F-4ECD-81BF-67FF73FC9B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6687D8B7-8C7C-4035-A8AB-CF3B36FBA7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="146">
   <si>
     <t>index</t>
   </si>
@@ -158,12 +158,824 @@
     <t>暂无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>中垦天宁牧业有限公司</t>
+  </si>
+  <si>
+    <t>临泽县德源农庄高效农业合作社</t>
+  </si>
+  <si>
+    <t>乐亭投资集团有限公司</t>
+  </si>
+  <si>
+    <t>京山绿丰家庭农场有限公司</t>
+  </si>
+  <si>
+    <t>凯盛浩丰农业有限公司</t>
+  </si>
+  <si>
+    <t>华维节水科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>抚松县参王植保有限责任公司</t>
+  </si>
+  <si>
+    <t>捷佳润科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>新泰市天信农牧发展有限公司</t>
+  </si>
+  <si>
+    <t>望家欢农产品集团有限公司</t>
+  </si>
+  <si>
+    <t>湘丰茶业集团有限公司</t>
+  </si>
+  <si>
+    <t>牧同科技股份有限公司</t>
+  </si>
+  <si>
+    <t>玖兴农牧（涞源）有限公司</t>
+  </si>
+  <si>
+    <t>现代牧业（集团）有限公司</t>
+  </si>
+  <si>
+    <t>禾丰食品股份有限公司</t>
+  </si>
+  <si>
+    <t>秭归县屈姑食品有限公司</t>
+  </si>
+  <si>
+    <t>通海锦海农业科技发展有限公司</t>
+  </si>
+  <si>
+    <t>邛崃市新农开发建设有限公司</t>
+  </si>
+  <si>
+    <t>门源县现代农业发展有限公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>三河市香丰肥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省廊坊市三河市香丰街1号</t>
+  </si>
+  <si>
+    <t>0316-3158999</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/466917033</t>
+  </si>
+  <si>
+    <t>河北省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>廊坊市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>上高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>县茶杉禽业有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江西省宜春市上高县徐家渡镇花山路86号（承诺申报）</t>
+  </si>
+  <si>
+    <t>0795-2525225</t>
+  </si>
+  <si>
+    <t>江西省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜春市</t>
+  </si>
+  <si>
+    <t>江西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/356661342</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>中国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>热带农业科学院科技信息研究所</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海南省海口市龙华区学院路4号</t>
+  </si>
+  <si>
+    <t>海南省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海口市</t>
+  </si>
+  <si>
+    <t>海南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3097985481</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3119239236</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区中宁县恩和镇</t>
+  </si>
+  <si>
+    <t>宁夏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中宁县</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3065714287</t>
+  </si>
+  <si>
+    <t>甘肃省张掖市临泽县鸭暖镇五泉村六社</t>
+  </si>
+  <si>
+    <t>甘肃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张掖市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3293909748</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>河北唐山市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>乐亭县乐安街道茂源街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>158</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唐山市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/2328566008</t>
+  </si>
+  <si>
+    <t>湖北省荆门市京山市罗店镇麻城村二组</t>
+  </si>
+  <si>
+    <t>荆门市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯盛浩丰农业集团有限公司</t>
+  </si>
+  <si>
+    <t>山东省青岛市莱西市院上镇凯盛浩丰路1号</t>
+  </si>
+  <si>
+    <t>青岛市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海市金山区亭林镇南亭公路5859号2幢</t>
+  </si>
+  <si>
+    <t>上海华维可控农业科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3269402188</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>大庄园肉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业集团股份有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑龙江省肇东市经济开发区创业大道490号</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3418761808</t>
+  </si>
+  <si>
+    <t>肇东市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑龙江</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>宁南</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>县南丝路集团有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/354051731</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>四川省凉山宁南</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>县宁远镇南丝路北延段南丝路大厦</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉山州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>微山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>县南四湖渔业有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省济宁市微山县经济开发区青山路南侧</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/2340180309</t>
+  </si>
+  <si>
+    <t>济宁市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/222035811</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>吉林省白山市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>抚松工业集中区苏州创业园</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>＃厂房</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白山市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3469127654</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>广西</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>南宁市西</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>乡塘区高新区创新路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>号楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>层</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南宁市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山东省泰安市新泰市楼德镇东村会馆大街东首</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/2310154658</t>
+  </si>
+  <si>
+    <t>泰安市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市福田区梅林街道梅都社区中康路136号深圳新一代产业园6栋1301-1304、301</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/2360028062</t>
+  </si>
+  <si>
+    <t>深圳市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖南省长沙县金井镇湘丰村</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3164214401</t>
+  </si>
+  <si>
+    <t>长沙市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西省大同市云冈经济技术开发区塔山产业园区</t>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3402731302</t>
+  </si>
+  <si>
+    <t>大同市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3337636191</t>
+  </si>
+  <si>
+    <t>河北省保定市涞源县经济开发区纬十七路一号（曲村北）、金家井乡金家井村北</t>
+  </si>
+  <si>
+    <t>保定市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/5234665</t>
+  </si>
+  <si>
+    <t>辽宁省沈阳市沈北新区辉山大街169号</t>
+  </si>
+  <si>
+    <t>沈阳市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辽宁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/554993671</t>
+  </si>
+  <si>
+    <t>湖北省宜昌市秭归县茅坪镇金缸城村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜昌市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/662445988</t>
+  </si>
+  <si>
+    <t>云南省玉溪市通海县河西镇河西村贾梨园</t>
+  </si>
+  <si>
+    <t>玉溪市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/386305357</t>
+  </si>
+  <si>
+    <t>安徽省马鞍山市经济技术开发区红旗南路123号</t>
+  </si>
+  <si>
+    <t>马鞍山市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3059961624</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四川省成都市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>邛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>崃市临邛街道办文昌街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>121</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成都</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁力市金新农生态农牧有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/2413896014</t>
+  </si>
+  <si>
+    <t>黑龙江省伊春市铁力市铁力镇工业园区饲料厂办公楼</t>
+  </si>
+  <si>
+    <t>伊春市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tianyancha.com/company/3165656753</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>青海省海北藏族自治州门源回族自治</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>县疙瘩滩生物园区农牧产业孵化园二楼</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海北藏族自治州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青海</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -225,6 +1037,83 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="MS Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -254,6 +1143,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -637,6 +1534,616 @@
         <v>16</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="35" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="G35" s="2"/>
@@ -649,6 +2156,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot-2024-06-hand.xlsx
+++ b/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot-2024-06-hand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\data-tidy\hack-tianyan\hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6687D8B7-8C7C-4035-A8AB-CF3B36FBA7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B1198F-AAC0-4951-A708-631DDE70F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="143">
   <si>
     <t>index</t>
   </si>
@@ -250,10 +250,6 @@
     <t>https://www.tianyancha.com/company/466917033</t>
   </si>
   <si>
-    <t>河北省</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>廊坊市</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,10 +289,6 @@
     <t>0795-2525225</t>
   </si>
   <si>
-    <t>江西省</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宜春市</t>
   </si>
   <si>
@@ -333,10 +325,6 @@
   </si>
   <si>
     <t>海南省海口市龙华区学院路4号</t>
-  </si>
-  <si>
-    <t>海南省</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>海口市</t>
@@ -1554,13 +1542,13 @@
         <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1568,28 +1556,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="I5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1597,25 +1585,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="I6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1629,16 +1617,19 @@
         <v>19</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1652,19 +1643,19 @@
         <v>20</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1678,16 +1669,19 @@
         <v>21</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1701,16 +1695,19 @@
         <v>22</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1721,16 +1718,19 @@
         <v>23</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>74</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1741,13 +1741,16 @@
         <v>24</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>16</v>
@@ -1758,22 +1761,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="I13" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="F13" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,22 +1787,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="I14" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1804,22 +1813,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1833,16 +1845,19 @@
         <v>25</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1856,16 +1871,19 @@
         <v>26</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1879,16 +1897,19 @@
         <v>27</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,16 +1923,19 @@
         <v>28</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F19" t="s">
-        <v>106</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1925,16 +1949,19 @@
         <v>29</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F20" t="s">
-        <v>110</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1948,16 +1975,19 @@
         <v>30</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F21" t="s">
-        <v>114</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1971,16 +2001,19 @@
         <v>31</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1994,16 +2027,19 @@
         <v>32</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F23" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2017,16 +2053,19 @@
         <v>33</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2040,16 +2079,19 @@
         <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>124</v>
+        <v>121</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2063,16 +2105,19 @@
         <v>35</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2086,16 +2131,19 @@
         <v>36</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -2103,22 +2151,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" t="s">
-        <v>139</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.4">
@@ -2132,16 +2183,19 @@
         <v>37</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>142</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
